--- a/dist/downloads/model-documents/openbmb-minicpm-moe-8x2b.xlsx
+++ b/dist/downloads/model-documents/openbmb-minicpm-moe-8x2b.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R992eab59e4e74bfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="Rc0d042148ef94ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R01a31b661f504689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R291da66b5d864051"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1061,7 +1061,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -2441,7 +2441,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" hidden="0" customHeight="1">
@@ -3821,7 +3821,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="24" hidden="0" customHeight="1">
@@ -5201,7 +5201,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="24" hidden="0" customHeight="1">
@@ -6581,7 +6581,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD66" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="24" hidden="0" customHeight="1">
@@ -7961,7 +7961,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD81" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="24" hidden="0" customHeight="1">
@@ -9341,7 +9341,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD96" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="24" hidden="0" customHeight="1">
@@ -10721,7 +10721,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD111" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="24" hidden="0" customHeight="1">
@@ -12101,7 +12101,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD126" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="24" hidden="0" customHeight="1">
@@ -13481,7 +13481,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD141" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="24" hidden="0" customHeight="1">
@@ -14861,7 +14861,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD156" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="24" hidden="0" customHeight="1">
@@ -16241,7 +16241,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD171" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="24" hidden="0" customHeight="1">
@@ -17621,7 +17621,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD186" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="24" hidden="0" customHeight="1">
@@ -19001,7 +19001,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD201" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="24" hidden="0" customHeight="1">
@@ -20381,7 +20381,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD216" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="24" hidden="0" customHeight="1">
@@ -21761,7 +21761,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD231" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="24" hidden="0" customHeight="1">
@@ -23141,7 +23141,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD246" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="24" hidden="0" customHeight="1">
@@ -24521,7 +24521,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD261" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="24" hidden="0" customHeight="1">
@@ -25901,7 +25901,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD276" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="24" hidden="0" customHeight="1">
@@ -27281,7 +27281,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD291" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="24" hidden="0" customHeight="1">
@@ -28661,7 +28661,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD306" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="307" ht="24" hidden="0" customHeight="1">
@@ -30041,7 +30041,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD321" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="322" ht="24" hidden="0" customHeight="1">
@@ -31421,7 +31421,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD336" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="337" ht="24" hidden="0" customHeight="1">
@@ -32801,7 +32801,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD351" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="352" ht="24" hidden="0" customHeight="1">
@@ -34181,7 +34181,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD366" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="367" ht="24" hidden="0" customHeight="1">
@@ -35561,7 +35561,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD381" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="24" hidden="0" customHeight="1">
@@ -36941,7 +36941,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD396" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="24" hidden="0" customHeight="1">
@@ -38321,7 +38321,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD411" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="412" ht="24" hidden="0" customHeight="1">
@@ -39701,7 +39701,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD426" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="427" ht="24" hidden="0" customHeight="1">
@@ -41081,7 +41081,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD441" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="442" ht="24" hidden="0" customHeight="1">
@@ -42461,7 +42461,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD456" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="457" ht="24" hidden="0" customHeight="1">
@@ -43841,7 +43841,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD471" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="472" ht="24" hidden="0" customHeight="1">
@@ -45221,7 +45221,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD486" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="487" ht="24" hidden="0" customHeight="1">
@@ -46601,7 +46601,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD501" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="502" ht="24" hidden="0" customHeight="1">
@@ -47981,7 +47981,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD516" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="517" ht="24" hidden="0" customHeight="1">
@@ -49361,7 +49361,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD531" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="532" ht="24" hidden="0" customHeight="1">
@@ -50741,7 +50741,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD546" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="547" ht="24" hidden="0" customHeight="1">
@@ -52121,7 +52121,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD561" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="562" ht="24" hidden="0" customHeight="1">
@@ -53501,7 +53501,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD576" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="577" ht="24" hidden="0" customHeight="1">
@@ -54881,7 +54881,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD591" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="592" ht="24" hidden="0" customHeight="1">
@@ -56051,7 +56051,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -56200,7 +56200,7 @@
         </x:is>
       </x:c>
       <x:c r="C14" s="28" t="str">
-        <x:v>5760 / 不适用</x:v>
+        <x:v>5760 / 5760</x:v>
       </x:c>
       <x:c r="D14" s="28" t="str">
         <x:v>https://huggingface.co/openbmb/MiniCPM-MoE-8x2B/resolve/7495286593bc56a524a42e26eeaee5e185cb7f9c/config.json</x:v>
@@ -56315,7 +56315,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -56328,7 +56331,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -56814,8 +56820,8 @@
       <x:c r="E60" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -56823,6 +56829,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
